--- a/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="446">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -263,7 +263,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>act[classCode=ACT][moodCode=DEF]</t>
@@ -310,10 +310,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>HealthcareService.meta.id</t>
   </si>
   <si>
@@ -487,6 +494,9 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>HealthcareService.meta.tag</t>
   </si>
   <si>
@@ -603,39 +613,29 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>HealthcareService.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t>as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization}
+    <t>HealthcareService.extension:as-ext-authorization</t>
+  </si>
+  <si>
+    <t>as-ext-authorization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization}
 </t>
   </si>
   <si>
-    <t>AS HealthcareService Autorization Extension</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations  des activités sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels lourds autorisés.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
+    <t>AS Authorization Extension</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations des activités (HealthcareService) sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels (Device) lourds autorisés.</t>
   </si>
   <si>
     <t>HealthcareService.modifierExtension</t>
@@ -835,7 +835,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -863,6 +871,10 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
@@ -947,6 +959,9 @@
   </si>
   <si>
     <t>The specific type of service that may be delivered or performed.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J131-CategorieActiviteSanitaireRegulee-RASS/FHIR/JDV-J131-CategorieActiviteSanitaireRegulee-RASS</t>
@@ -982,6 +997,9 @@
     <t>The location(s) where this healthcare service may be provided.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>.location.role[classCode=SDLOC]</t>
   </si>
   <si>
@@ -995,6 +1013,9 @@
   </si>
   <si>
     <t>Further description of the service as it would be presented to a consumer while searching.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>.name</t>
@@ -1028,6 +1049,9 @@
     <t>Extra details about the service that can't be placed in the other fields.</t>
   </si>
   <si>
+    <t>Systems are not required to have markdown support, so the text should be readable without markdown processing. The markdown syntax is GFM - see https://github.github.com/gfm/</t>
+  </si>
+  <si>
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].text</t>
   </si>
   <si>
@@ -1044,6 +1068,13 @@
     <t>If there is a photo/symbol associated with this HealthcareService, it may be included here to facilitate quick identification of the service in a list.</t>
   </si>
   <si>
+    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
+  </si>
+  <si>
     <t>.actrelationship[typeCode=SBJ].observation.value</t>
   </si>
   <si>
@@ -1063,6 +1094,10 @@
     <t>If this is empty, then refer to the location's contacts.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+cpt-2:A system is required if a value is provided. {value.empty() or system.exists()}</t>
+  </si>
+  <si>
     <t>.telecom</t>
   </si>
   <si>
@@ -1210,6 +1245,9 @@
     <t>When using this property it indicates that the service is available with this language, it is not derived from the practitioners, and not all are required to use this language, just that this language is available while scheduling.</t>
   </si>
   <si>
+    <t>CD</t>
+  </si>
+  <si>
     <t>HealthcareService.referralMethod</t>
   </si>
   <si>
@@ -1363,6 +1401,9 @@
   </si>
   <si>
     <t>Technical endpoints providing access to services operated for the specific healthcare services defined at this resource.</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
 </sst>
 </file>
@@ -1682,9 +1723,9 @@
   <dimension ref="A1:AL70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="63.55078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.46484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.1328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="36.5703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.67578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2145,13 +2186,13 @@
         <v>84</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>75</v>
@@ -2159,10 +2200,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2185,13 +2226,13 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2242,7 +2283,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -2257,7 +2298,7 @@
         <v>75</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>75</v>
@@ -2265,14 +2306,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2291,16 +2332,16 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2338,19 +2379,19 @@
         <v>75</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -2359,13 +2400,13 @@
         <v>77</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL6" t="s" s="2">
         <v>75</v>
@@ -2373,13 +2414,13 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>75</v>
@@ -2401,13 +2442,13 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2458,7 +2499,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -2467,10 +2508,10 @@
         <v>77</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -2481,10 +2522,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2510,13 +2551,13 @@
         <v>86</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2566,7 +2607,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -2575,13 +2616,13 @@
         <v>84</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>75</v>
@@ -2589,10 +2630,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2615,16 +2656,16 @@
         <v>85</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2674,7 +2715,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -2683,13 +2724,13 @@
         <v>84</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>75</v>
@@ -2697,10 +2738,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2723,16 +2764,16 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2782,7 +2823,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2791,13 +2832,13 @@
         <v>84</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>75</v>
@@ -2805,10 +2846,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2831,16 +2872,16 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2890,7 +2931,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -2899,13 +2940,13 @@
         <v>77</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>75</v>
@@ -2913,10 +2954,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2939,16 +2980,16 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2974,13 +3015,13 @@
         <v>75</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>75</v>
@@ -2998,7 +3039,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3007,13 +3048,13 @@
         <v>77</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>75</v>
@@ -3021,10 +3062,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3047,16 +3088,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3082,13 +3123,13 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -3106,7 +3147,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3115,13 +3156,13 @@
         <v>77</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>75</v>
@@ -3129,10 +3170,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3155,16 +3196,16 @@
         <v>85</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3214,7 +3255,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3223,13 +3264,13 @@
         <v>84</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>75</v>
@@ -3237,10 +3278,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3263,16 +3304,16 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3298,13 +3339,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -3322,7 +3363,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3331,13 +3372,13 @@
         <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>75</v>
@@ -3345,14 +3386,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3371,16 +3412,16 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3430,7 +3471,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3439,13 +3480,13 @@
         <v>84</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>75</v>
@@ -3453,14 +3494,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3479,16 +3520,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3538,7 +3579,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3553,7 +3594,7 @@
         <v>75</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>75</v>
@@ -3561,14 +3602,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3587,15 +3628,17 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>190</v>
+        <v>108</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -3632,17 +3675,19 @@
         <v>75</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="AC18" s="2"/>
+        <v>111</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>112</v>
+      </c>
       <c r="AD18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3651,13 +3696,13 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>75</v>
@@ -3665,13 +3710,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>75</v>
@@ -3693,13 +3738,13 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3750,7 +3795,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3759,10 +3804,10 @@
         <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>75</v>
@@ -3780,7 +3825,7 @@
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3799,7 +3844,7 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>200</v>
@@ -3808,7 +3853,7 @@
         <v>201</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O20" t="s" s="2">
         <v>202</v>
@@ -3848,16 +3893,16 @@
         <v>75</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>203</v>
@@ -3869,13 +3914,13 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>75</v>
@@ -3963,7 +4008,7 @@
         <v>75</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>204</v>
@@ -3975,10 +4020,10 @@
         <v>77</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>210</v>
@@ -4083,10 +4128,10 @@
         <v>77</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>210</v>
@@ -4123,13 +4168,13 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4180,7 +4225,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4195,7 +4240,7 @@
         <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>75</v>
@@ -4210,7 +4255,7 @@
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4229,16 +4274,16 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4276,19 +4321,19 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4297,13 +4342,13 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>75</v>
@@ -4337,7 +4382,7 @@
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>221</v>
@@ -4407,10 +4452,10 @@
         <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>229</v>
@@ -4484,7 +4529,7 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y26" t="s" s="2">
         <v>237</v>
@@ -4517,10 +4562,10 @@
         <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>229</v>
@@ -4557,7 +4602,7 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>242</v>
@@ -4627,10 +4672,10 @@
         <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>249</v>
@@ -4667,7 +4712,7 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>252</v>
@@ -4735,10 +4780,10 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>257</v>
@@ -4783,7 +4828,9 @@
       <c r="M29" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="N29" s="2"/>
+      <c r="N29" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
@@ -4832,7 +4879,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4841,13 +4888,13 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>96</v>
+        <v>265</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4855,10 +4902,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4881,16 +4928,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4940,7 +4987,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4949,13 +4996,13 @@
         <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
@@ -4963,10 +5010,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4989,23 +5036,23 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q31" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="R31" t="s" s="2">
         <v>75</v>
@@ -5050,7 +5097,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5059,24 +5106,24 @@
         <v>84</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5099,16 +5146,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5158,7 +5205,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5167,13 +5214,13 @@
         <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
@@ -5181,14 +5228,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5210,13 +5257,13 @@
         <v>232</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5246,7 +5293,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>75</v>
@@ -5264,7 +5311,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5273,28 +5320,28 @@
         <v>77</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5316,12 +5363,14 @@
         <v>232</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5350,7 +5399,7 @@
       </c>
       <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5368,7 +5417,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5377,13 +5426,13 @@
         <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
@@ -5391,10 +5440,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5420,12 +5469,14 @@
         <v>232</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -5454,7 +5505,7 @@
       </c>
       <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5472,7 +5523,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5481,13 +5532,13 @@
         <v>77</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
@@ -5495,10 +5546,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5521,15 +5572,17 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5578,7 +5631,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5587,24 +5640,24 @@
         <v>77</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5627,15 +5680,17 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5684,7 +5739,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5693,13 +5748,13 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
@@ -5707,10 +5762,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5733,16 +5788,16 @@
         <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5792,7 +5847,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5801,13 +5856,13 @@
         <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5815,10 +5870,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5841,15 +5896,17 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5898,7 +5955,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5907,13 +5964,13 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5921,10 +5978,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5947,15 +6004,17 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -6004,7 +6063,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6013,13 +6072,13 @@
         <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>96</v>
+        <v>337</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -6027,10 +6086,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6053,16 +6112,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6112,7 +6171,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -6121,13 +6180,13 @@
         <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>96</v>
+        <v>344</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -6135,10 +6194,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6161,16 +6220,16 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6220,7 +6279,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6229,13 +6288,13 @@
         <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>75</v>
@@ -6243,10 +6302,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6272,13 +6331,13 @@
         <v>232</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6304,13 +6363,13 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6328,7 +6387,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6337,13 +6396,13 @@
         <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6351,10 +6410,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6377,13 +6436,13 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6434,7 +6493,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6443,13 +6502,13 @@
         <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6457,10 +6516,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6483,13 +6542,13 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6540,7 +6599,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6555,7 +6614,7 @@
         <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6563,14 +6622,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6589,16 +6648,16 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6636,19 +6695,19 @@
         <v>75</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6657,13 +6716,13 @@
         <v>77</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6671,14 +6730,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6697,16 +6756,16 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O47" t="s" s="2">
         <v>202</v>
@@ -6758,7 +6817,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6767,13 +6826,13 @@
         <v>77</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6781,10 +6840,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6810,12 +6869,14 @@
         <v>232</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6840,10 +6901,10 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>75</v>
@@ -6864,7 +6925,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6873,13 +6934,13 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6887,10 +6948,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6913,16 +6974,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6972,7 +7033,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6981,13 +7042,13 @@
         <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
@@ -6995,10 +7056,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7024,13 +7085,13 @@
         <v>232</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7056,13 +7117,13 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -7080,7 +7141,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7089,13 +7150,13 @@
         <v>77</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
@@ -7103,10 +7164,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7132,13 +7193,13 @@
         <v>232</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7168,7 +7229,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -7186,7 +7247,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7195,13 +7256,13 @@
         <v>77</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>75</v>
@@ -7209,10 +7270,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7238,13 +7299,13 @@
         <v>232</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7270,13 +7331,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7294,7 +7355,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7303,13 +7364,13 @@
         <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>75</v>
+        <v>393</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>75</v>
@@ -7317,10 +7378,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7346,12 +7407,14 @@
         <v>232</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>75</v>
@@ -7376,13 +7439,13 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7400,7 +7463,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7409,13 +7472,13 @@
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>75</v>
@@ -7423,10 +7486,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7449,13 +7512,13 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7506,7 +7569,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7515,13 +7578,13 @@
         <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7529,10 +7592,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7555,16 +7618,16 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7614,7 +7677,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7623,13 +7686,13 @@
         <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>75</v>
@@ -7637,10 +7700,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7663,13 +7726,13 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7720,7 +7783,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7735,7 +7798,7 @@
         <v>75</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>75</v>
@@ -7743,14 +7806,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7769,16 +7832,16 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -7816,19 +7879,19 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7837,13 +7900,13 @@
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
@@ -7851,14 +7914,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7877,16 +7940,16 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>202</v>
@@ -7938,7 +8001,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7947,13 +8010,13 @@
         <v>77</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>75</v>
@@ -7961,10 +8024,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7987,15 +8050,17 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>75</v>
@@ -8023,10 +8088,10 @@
         <v>225</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -8044,7 +8109,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -8053,13 +8118,13 @@
         <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>75</v>
@@ -8067,10 +8132,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8093,13 +8158,13 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8150,7 +8215,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8159,13 +8224,13 @@
         <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>75</v>
@@ -8173,10 +8238,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8199,16 +8264,16 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8258,7 +8323,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8267,13 +8332,13 @@
         <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8281,10 +8346,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8307,16 +8372,16 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8366,7 +8431,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8375,13 +8440,13 @@
         <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -8389,10 +8454,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8415,13 +8480,13 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8472,7 +8537,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8481,13 +8546,13 @@
         <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -8495,10 +8560,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8521,13 +8586,13 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8578,7 +8643,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -8593,7 +8658,7 @@
         <v>75</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>75</v>
@@ -8601,14 +8666,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8627,16 +8692,16 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8674,19 +8739,19 @@
         <v>75</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -8695,13 +8760,13 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>75</v>
@@ -8709,14 +8774,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -8735,16 +8800,16 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>202</v>
@@ -8796,7 +8861,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -8805,13 +8870,13 @@
         <v>77</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>75</v>
@@ -8819,10 +8884,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8845,15 +8910,17 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
@@ -8902,7 +8969,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>84</v>
@@ -8911,13 +8978,13 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>75</v>
@@ -8925,10 +8992,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8954,12 +9021,14 @@
         <v>260</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -9008,7 +9077,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9017,13 +9086,13 @@
         <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>96</v>
+        <v>265</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>75</v>
@@ -9031,10 +9100,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9057,15 +9126,17 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9114,7 +9185,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9123,13 +9194,13 @@
         <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>75</v>
@@ -9137,10 +9208,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9163,15 +9234,17 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9220,7 +9293,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9229,13 +9302,13 @@
         <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>96</v>
+        <v>274</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>102</v>
+        <v>445</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>75</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dp-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
